--- a/AAAGameData/DataTables/Text/ObjectiveTable.xlsx
+++ b/AAAGameData/DataTables/Text/ObjectiveTable.xlsx
@@ -408,7 +408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.140625" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>行动目标定义表</t>
+          <t>目标定义表</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
